--- a/artfynd/A 22491-2026 artfynd.xlsx
+++ b/artfynd/A 22491-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90839847</v>
+        <v>91133155</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Haga_SÖ, öster om Locknesjön, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495451.9472591965</v>
+        <v>495564</v>
       </c>
       <c r="R2" t="n">
-        <v>6983658.892063908</v>
+        <v>6983709</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-08-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90839849</v>
+        <v>90839847</v>
       </c>
       <c r="B3" t="n">
-        <v>95661</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495498.9318462342</v>
+        <v>495452</v>
       </c>
       <c r="R3" t="n">
-        <v>6983723.842289989</v>
+        <v>6983659</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +849,9 @@
           <t>2019-08-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90839855</v>
+        <v>90921822</v>
       </c>
       <c r="B4" t="n">
-        <v>95661</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,13 +922,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495485.1947205595</v>
+        <v>495502</v>
       </c>
       <c r="R4" t="n">
-        <v>6983667.029677638</v>
+        <v>6983661</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,19 +955,9 @@
           <t>2019-08-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>90921822</v>
+        <v>91133157</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,17 +1024,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Haga_SÖ, öster om Locknesjön, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495502.0322302064</v>
+        <v>495564</v>
       </c>
       <c r="R5" t="n">
-        <v>6983661.095855735</v>
+        <v>6983709</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,19 +1061,9 @@
           <t>2019-08-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91133155</v>
+        <v>91133166</v>
       </c>
       <c r="B6" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1199,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495564.017133421</v>
+        <v>495494</v>
       </c>
       <c r="R6" t="n">
-        <v>6983709.204266516</v>
+        <v>6983766</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1232,19 +1167,9 @@
           <t>2019-08-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91133156</v>
+        <v>90839849</v>
       </c>
       <c r="B7" t="n">
-        <v>95661</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98137</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,14 +1236,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Haga_SÖ, öster om Locknesjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495564.017133421</v>
+        <v>495499</v>
       </c>
       <c r="R7" t="n">
-        <v>6983709.204266516</v>
+        <v>6983724</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1353,19 +1273,9 @@
           <t>2019-08-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91133157</v>
+        <v>90839855</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,34 +1322,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Haga_SÖ, öster om Locknesjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495564.017133421</v>
+        <v>495485</v>
       </c>
       <c r="R8" t="n">
-        <v>6983709.204266516</v>
+        <v>6983667</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1474,19 +1379,9 @@
           <t>2019-08-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,6 +1410,112 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>91133156</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Halbodarna_SÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>495564</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6983709</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-08-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-08-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>

--- a/artfynd/A 22491-2026 artfynd.xlsx
+++ b/artfynd/A 22491-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91133155</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839847</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90921822</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91133157</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91133166</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839849</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839855</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,8 +1560,23 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91133156</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>